--- a/2.RD_CGE/Input_WEB/240522_Non-CO2_coef.xlsx
+++ b/2.RD_CGE/Input_WEB/240522_Non-CO2_coef.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD56261-CBE9-4606-A020-5F38ABA24F51}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6287D874-5ADD-4E8E-B251-54D5AC90D2E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="4" xr2:uid="{D7C0429B-4257-4FFE-BA40-977622B0A6A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{D7C0429B-4257-4FFE-BA40-977622B0A6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="01_KOR" sheetId="1" r:id="rId1"/>
@@ -660,19 +660,35 @@
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="B12" s="2">
+        <v>8204.262518504509</v>
+      </c>
+      <c r="C12" s="2">
+        <v>733.12450420726589</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="B13" s="2">
+        <v>239.47765076427839</v>
+      </c>
+      <c r="C13" s="2">
+        <v>301.3216223270677</v>
+      </c>
+      <c r="D13" s="2">
+        <v>5.5479062073250682E-5</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -1198,19 +1214,35 @@
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="B12" s="2">
+        <v>13450.637263166316</v>
+      </c>
+      <c r="C12" s="2">
+        <v>26657.492677734062</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="B13" s="2">
+        <v>485.17603065023343</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3463.942091423236</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.68017364557670468</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -1730,19 +1762,35 @@
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="B12" s="2">
+        <v>4962.7219554264993</v>
+      </c>
+      <c r="C12" s="2">
+        <v>700.95119687423391</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.12964654885752874</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="B13" s="2">
+        <v>3.1228976674748847</v>
+      </c>
+      <c r="C13" s="2">
+        <v>157.75921750309791</v>
+      </c>
+      <c r="D13" s="2">
+        <v>8.1302637064849649E-4</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2262,19 +2310,35 @@
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="B12" s="2">
+        <v>33824.338308548977</v>
+      </c>
+      <c r="C12" s="2">
+        <v>75031.364339407417</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1.6630176944773494</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="B13" s="2">
+        <v>4223.7980596323323</v>
+      </c>
+      <c r="C13" s="2">
+        <v>12253.340824544197</v>
+      </c>
+      <c r="D13" s="2">
+        <v>10.274661055099319</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2795,19 +2859,35 @@
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="B12" s="2">
+        <v>10257.372258280879</v>
+      </c>
+      <c r="C12" s="2">
+        <v>441263.01468515792</v>
+      </c>
+      <c r="D12" s="2">
+        <v>19.525229521296644</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="B13" s="2">
+        <v>11488.516189352968</v>
+      </c>
+      <c r="C13" s="2">
+        <v>737959.72803762683</v>
+      </c>
+      <c r="D13" s="2">
+        <v>95.021065761688746</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -3334,19 +3414,35 @@
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="B12" s="2">
+        <v>32922.186179021664</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1535909.9893292747</v>
+      </c>
+      <c r="D12" s="2">
+        <v>945.61898915351458</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="B13" s="2">
+        <v>0.16640119757786362</v>
+      </c>
+      <c r="C13" s="2">
+        <v>919.7162799014244</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">

--- a/2.RD_CGE/Input_WEB/240522_Non-CO2_coef.xlsx
+++ b/2.RD_CGE/Input_WEB/240522_Non-CO2_coef.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6287D874-5ADD-4E8E-B251-54D5AC90D2E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31F3BA6-320C-400F-A941-62AFC502C5C9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{D7C0429B-4257-4FFE-BA40-977622B0A6A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" firstSheet="5" activeTab="5" xr2:uid="{D7C0429B-4257-4FFE-BA40-977622B0A6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="01_KOR" sheetId="1" r:id="rId1"/>

--- a/2.RD_CGE/Input_WEB/240522_Non-CO2_coef.xlsx
+++ b/2.RD_CGE/Input_WEB/240522_Non-CO2_coef.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31F3BA6-320C-400F-A941-62AFC502C5C9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DBDED8-C46A-4DBF-BFD5-6E1A2AB72E3D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" firstSheet="5" activeTab="5" xr2:uid="{D7C0429B-4257-4FFE-BA40-977622B0A6A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="750" firstSheet="3" activeTab="16" xr2:uid="{D7C0429B-4257-4FFE-BA40-977622B0A6A1}"/>
   </bookViews>
   <sheets>
     <sheet name="01_KOR" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,17 @@
     <sheet name="04_RUS" sheetId="4" r:id="rId4"/>
     <sheet name="05_MNG" sheetId="5" r:id="rId5"/>
     <sheet name="06_PRK" sheetId="6" r:id="rId6"/>
+    <sheet name="07_NAM" sheetId="7" r:id="rId7"/>
+    <sheet name="08_LAM" sheetId="8" r:id="rId8"/>
+    <sheet name="09_WEU" sheetId="9" r:id="rId9"/>
+    <sheet name="10_EEU" sheetId="10" r:id="rId10"/>
+    <sheet name="11_FSU" sheetId="11" r:id="rId11"/>
+    <sheet name="12_MEA" sheetId="12" r:id="rId12"/>
+    <sheet name="13_AFR" sheetId="13" r:id="rId13"/>
+    <sheet name="14_CPA" sheetId="14" r:id="rId14"/>
+    <sheet name="15_SAS" sheetId="15" r:id="rId15"/>
+    <sheet name="16_PAS" sheetId="16" r:id="rId16"/>
+    <sheet name="17_PAO" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="41">
   <si>
     <t>1.A.1.a</t>
   </si>
@@ -1096,6 +1107,5238 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06229C7F-18CD-4AE3-81CC-1ADC2255E670}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1548235-725E-4A54-A335-9FFB9246CDB7}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8C07DF-A179-4743-ACA7-E6A2DD82658E}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E594930-6707-4E3D-8DE1-4497C58CCB38}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3EFCDA-9206-45DF-8F4D-5B56B8892573}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19330DAF-E423-4707-94EE-D667286ADBF7}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{179F4576-8659-4278-8C44-EBFAB41F8BBF}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D49A20F-F559-41A7-9628-01B9BEBA8A00}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B3F80C3-1EBA-425B-92B7-FC622A554211}">
   <dimension ref="A1:E38"/>
@@ -3850,4 +9093,1969 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1420C27-D4B6-43F8-B06C-D82DF8DA964D}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{360FDE50-9B08-4BE8-8012-E104B8A033CA}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C747DEE4-BA16-4818-A52C-1DF61D4C8DD4}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>